--- a/cast_metal.xlsx
+++ b/cast_metal.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="Notes" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Letters – Fonts" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="Letters-Fonts" sheetId="2" r:id="rId5"/>
     <sheet state="visible" name="Letters – Custom Flat Face" sheetId="3" r:id="rId6"/>
     <sheet state="visible" name="Logos – Aluminum" sheetId="4" r:id="rId7"/>
     <sheet state="visible" name="Logos – Bronze" sheetId="5" r:id="rId8"/>
@@ -893,9 +893,6 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
-  <cols>
-    <col customWidth="1" min="1" max="6" width="12.63"/>
-  </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1"/>
@@ -2836,7 +2833,6 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="19.5"/>
-    <col customWidth="1" min="2" max="6" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -3882,7 +3878,6 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="19.5"/>
-    <col customWidth="1" min="2" max="6" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -9195,9 +9190,6 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
-  <cols>
-    <col customWidth="1" min="1" max="6" width="12.63"/>
-  </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="14" t="s">
@@ -15142,9 +15134,6 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
-  <cols>
-    <col customWidth="1" min="1" max="6" width="12.63"/>
-  </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="28" t="s">
@@ -45185,9 +45174,6 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
-  <cols>
-    <col customWidth="1" min="1" max="6" width="12.63"/>
-  </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="28" t="s">
@@ -59296,9 +59282,6 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
-  <cols>
-    <col customWidth="1" min="1" max="6" width="12.63"/>
-  </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="39" t="s">
@@ -61517,9 +61500,6 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
-  <cols>
-    <col customWidth="1" min="1" max="6" width="12.63"/>
-  </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="39" t="s">
@@ -63738,9 +63718,6 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
-  <cols>
-    <col customWidth="1" min="1" max="6" width="12.63"/>
-  </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="46" t="s">
@@ -67381,9 +67358,6 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
-  <cols>
-    <col customWidth="1" min="1" max="6" width="12.63"/>
-  </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="14" t="s">
